--- a/payroll.xlsx
+++ b/payroll.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,46 +524,57 @@
         <v>3000</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3000</v>
+        <v>2808</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1000</v>
+        <v>825</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>70</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5600</v>
+        <v>4833</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-22
-تأخير لمدة 3 دقيقة يوم 2026-07-02
-مراجعة يوم 2026-07-12 السبب Consecutive 'حضور' at 08:31 and 15:35
-مراجعة يوم 2026-07-16
-Achieved 92.9% of target (80%–&lt;100%) → 2000 × 0.8 = 1600
-zero accepts deductions: 0</t>
+          <t>غياب يوم 2026-08-19 خصم 96 من الاساسي غياب باذن خصم 96 جنيه 
+تأخير لمدة 1 دقيقة يوم 2026-08-12
+تأخير لمدة 3 دقيقة يوم 2026-08-17
+تأخير لمدة 13 دقيقة يوم 2026-08-20 خصم 0.5 نقاط تاخير نصف ساعه خصم نصف نقطة
+تأخير لمدة 3 دقيقة يوم 2026-08-26
+تأخير لمدة 9 دقيقة يوم 2026-08-27
+تأخير لمدة 6 دقيقة يوم 2026-08-31 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+مراجعة يوم 2026-08-03 السبب Consecutive 'حضور' at 08:30 and 13:10
+مراجعة يوم 2026-08-05
+مراجعة يوم 2026-08-08 السبب Consecutive 'إنصراف' at 17:31 and 17:39
+مراجعة يوم 2026-08-15
+مراجعة يوم 2026-09-01
+خصم 1 نقطة السبب  خصم نقطة creation fake في الشيت الاساسي 
+خصم 48 السبب يوم 3- 8 اذن نص يوم خصم 48 جنيه
+خصم 48 السبب يوم 3-  8 اذن نص يوم خصم 48 جنيه
+Achieved 75.7% of target (60%–&lt;80%) → 2000 × 0.6 = 1200
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>shahd</t>
+          <t>nadaf</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -572,54 +583,36 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3000</v>
+        <v>967.741935483871</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3000</v>
+        <v>967.741935483871</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1000</v>
+        <v>322.5806451612903</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1000</v>
+        <v>322.5806451612903</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4000</v>
+        <v>1290.322580645161</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-02
-غياب يوم 2026-07-08
-غياب يوم 2026-07-09
-غياب يوم 2026-07-11
-غياب يوم 2026-07-12
-غياب يوم 2026-07-13
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-غياب يوم 2026-07-26
-غياب يوم 2026-07-27
-غياب يوم 2026-07-28
-غياب يوم 2026-07-29
-غياب يوم 2026-07-30
-تأخير لمدة 265 دقيقة يوم 2026-07-05
-zero accepts deductions: 0</t>
+          <t>مراجعة يوم 2026-08-31 السبب Consecutive 'إنصراف' at 17:32 and 17:38
+مراجعة يوم 2026-09-01
+Target is zero or invalid → 0
+work days: 10
+zero accepts deductions: 1.0</t>
         </is>
       </c>
     </row>
@@ -649,24 +642,25 @@
         <v>1000</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>875</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n">
-        <v>12</v>
+        <v/>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3875</v>
+        <v>4000</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-13
-مراجعة يوم 2026-07-08 السبب Consecutive 'إنصراف' at 17:34 and 17:43
-Active count 12 &lt; 25 → 0
-zero accepts deductions: 1.25</t>
+          <t>مراجعة يوم 2026-08-23
+مراجعة يوم 2026-08-31
+مراجعة يوم 2026-09-01
+Active count nan outside ranges → 0
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
@@ -690,42 +684,47 @@
         <v>3000</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3000</v>
+        <v>2904</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>5125</v>
+        <v>5404</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-06
-غياب يوم 2026-07-08
-تأخير لمدة 13 دقيقة يوم 2026-07-11
-مراجعة يوم 2026-07-02
-مراجعة يوم 2026-07-30 السبب Consecutive 'حضور' at 08:11 and 17:30
-Achieved 68.6% of target (60%–&lt;80%) → 2000 × 0.6 = 1200
-zero accepts deductions: 0.75</t>
+          <t>غياب يوم 2026-08-23 خصم 96 من الاساسي غياب باذن خصم 96 جنيه
+غياب يوم 2026-08-24
+غياب يوم 2026-08-25
+غياب يوم 2026-08-26
+تأخير لمدة 13 دقيقة يوم 2026-08-03 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 5 دقيقة يوم 2026-08-10 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 6 دقيقة يوم 2026-08-18 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 1 دقيقة يوم 2026-08-29
+مراجعة يوم 2026-08-16 السبب Consecutive 'إنصراف' at 17:34 and 17:46
+مراجعة يوم 2026-09-01
+Achieved 85.0% of target (80%–&lt;100%) → 2000 × 0.8 = 1600
+zero accepts deductions: 1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>lobna</t>
+          <t>hayamayman</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -742,7 +741,7 @@
         <v>3000</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3000</v>
+        <v>2808</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1000</v>
@@ -754,41 +753,28 @@
         <v>45</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4000</v>
+        <v>5008</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-12
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-غياب يوم 2026-07-26
-غياب يوم 2026-07-27
-غياب يوم 2026-07-28
-غياب يوم 2026-07-29
-غياب يوم 2026-07-30
-Achieved 48.9% of target (&lt;60%) → 0
-zero accepts deductions: 0</t>
+          <t>غياب يوم 2026-08-22 خصم 96 من الاساسي غياب باذن خصم 96
+غياب يوم 2026-08-23 خصم 96 من الاساسي غياب باذن خصم 96
+مراجعة يوم 2026-09-01
+Achieved 64.4% of target (60%–&lt;80%) → 2000 × 0.6 = 1200
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>basant</t>
+          <t>bsantmohammed</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -814,10 +800,10 @@
         <v>1000</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -827,38 +813,26 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-01
-غياب يوم 2026-07-05
-غياب يوم 2026-07-06
-غياب يوم 2026-07-08
-غياب يوم 2026-07-09
-غياب يوم 2026-07-11
-غياب يوم 2026-07-12
-غياب يوم 2026-07-13
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-غياب يوم 2026-07-26
-غياب يوم 2026-07-27
-غياب يوم 2026-07-28
-غياب يوم 2026-07-29
-غياب يوم 2026-07-30
-Achieved 22.0% of target (&lt;60%) → 0
-zero accepts deductions: 0</t>
+          <t>غياب يوم 2026-08-11
+غياب يوم 2026-08-12
+غياب يوم 2026-08-13
+غياب يوم 2026-08-15
+غياب يوم 2026-08-16
+غياب يوم 2026-08-17
+غياب يوم 2026-08-18
+غياب يوم 2026-08-19
+غياب يوم 2026-08-20
+مراجعة يوم 2026-08-27
+مراجعة يوم 2026-09-01
+Achieved 55.0% of target (&lt;60%) → 0
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>hayamayman</t>
+          <t>mennaahmed</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -875,41 +849,44 @@
         <v>3000</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3000</v>
+        <v>1808</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4000</v>
+        <v>2708</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-مراجعة يوم 2026-07-13
-مراجعة يوم 2026-07-28 السبب Consecutive 'إنصراف' at 11:00 and 12:56 | Consecutive 'إنصراف' at 12:56 and 17:32
-Achieved 48.9% of target (&lt;60%) → 0
-zero accepts deductions: 0</t>
+          <t>غياب يوم 2026-08-01 خصم 96 من الاساسي غياب باذن خصم 96
+غياب يوم 2026-08-02 خصم 96 من الاساسي غياب باذن خصم 96
+تأخير لمدة 1 دقيقة يوم 2026-08-16
+تأخير لمدة 38 دقيقة يوم 2026-08-18 تاخير نصف ساعه خصم نصف نقطة
+تأخير لمدة 2 دقيقة يوم 2026-08-19
+مراجعة يوم 2026-09-01
+خصم 1000 السبب سلفه 1000 جنيه يوم 23 - 8 
+Achieved 50.0% of target (&lt;60%) → 0
+zero accepts deductions: 4.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>bsantmohammed</t>
+          <t>ayaahmed</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -926,41 +903,49 @@
         <v>3000</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3000</v>
+        <v>2260</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1000</v>
+        <v>775</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>5600</v>
+        <v>3035</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-16
-مراجعة يوم 2026-07-08 السبب Consecutive 'إنصراف' at 17:34 and 17:40
-مراجعة يوم 2026-07-11
-مراجعة يوم 2026-07-22
-Achieved 82.5% of target (80%–&lt;100%) → 2000 × 0.8 = 1600
-zero accepts deductions: 0</t>
+          <t>غياب يوم 2026-08-26 خصم 96 من الاساسي غياب باذن خصم 96 جنيه
+تأخير لمدة 207 دقيقة يوم 2026-08-01 خصم 96 من الاساسي خصم 96 جنيه تاخير نص يوم بدون اذن
+تأخير لمدة 10 دقيقة يوم 2026-08-02 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 5 دقيقة يوم 2026-08-03 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 1 دقيقة يوم 2026-08-16
+تأخير لمدة 3 دقيقة يوم 2026-08-17
+مراجعة يوم 2026-08-09
+مراجعة يوم 2026-08-23 السبب Consecutive 'حضور' at 08:31 and 17:31
+مراجعة يوم 2026-09-01
+خصم 48 السبب خصم 48 جنيه اذن نصف يوم تاريخ 22 - 8
+خصم 1 نقطة السبب خصم نقطة عدم اتباع التعليمات المكالمة بتاريخ 19 - 8
+خصم 500 السبب سلفة 500 جنيه بتاريخ 27 - 8
+Achieved 35.0% of target (&lt;60%) → 0
+zero accepts deductions: 3.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>mennaahmed</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -977,44 +962,47 @@
         <v>3000</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3000</v>
+        <v>2808</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>975</v>
+        <v>925</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3975</v>
+        <v>3733</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-09
-غياب يوم 2026-07-25
-غياب يوم 2026-07-26
-غياب يوم 2026-07-27
-غياب يوم 2026-07-28
-غياب يوم 2026-07-29
-غياب يوم 2026-07-30
-Achieved 47.5% of target (&lt;60%) → 0
-zero accepts deductions: 0.25</t>
+          <t>غياب يوم 2026-08-01 خصم 96 من الاساسي غياب باذن خصم 96
+غياب يوم 2026-08-05 خصم 96 من الاساسي غياب باذن خصم 96
+تأخير لمدة 10 دقيقة يوم 2026-08-02 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 5 دقيقة يوم 2026-08-03 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 1 دقيقة يوم 2026-08-16
+تأخير لمدة 3 دقيقة يوم 2026-08-17
+تأخير لمدة 2 دقيقة يوم 2026-08-19
+تأخير لمدة 2 دقيقة يوم 2026-08-26
+مراجعة يوم 2026-08-13
+مراجعة يوم 2026-09-01
+Achieved 55.0% of target (&lt;60%) → 0
+zero accepts deductions: 1.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ayaahmed</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1031,45 +1019,42 @@
         <v>3000</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3000</v>
+        <v>2904</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>40</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n">
-        <v>8</v>
+        <v/>
       </c>
       <c r="J11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>3950</v>
+        <v>3904</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-05
-تأخير لمدة 21 دقيقة يوم 2026-07-01
-تأخير لمدة 203 دقيقة يوم 2026-07-07
-تأخير لمدة 5 دقيقة يوم 2026-07-16
-تأخير لمدة 235 دقيقة يوم 2026-07-30
-مراجعة يوم 2026-07-13
-مراجعة يوم 2026-07-26 السبب Consecutive 'إنصراف' at 17:32 and 17:46
-مراجعة يوم 2026-07-28
-Achieved 20.0% of target (&lt;60%) → 0
-zero accepts deductions: 0.5</t>
+          <t>غياب يوم 2026-08-08 خصم 96 من الاساسي غياب يوم باذن خصم 96
+مراجعة يوم 2026-08-02 السبب Consecutive 'إنصراف' at 17:32 and 17:40
+مراجعة يوم 2026-08-06
+مراجعة يوم 2026-08-13
+مراجعة يوم 2026-08-18 السبب Consecutive 'إنصراف' at 13:00 and 15:00 | Consecutive 'إنصراف' at 15:00 and 17:30
+مراجعة يوم 2026-08-29
+مراجعة يوم 2026-09-01
+Active count nan outside ranges → 0
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>nadamohammed</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1086,39 +1071,45 @@
         <v>3000</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3000</v>
+        <v>1974</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>925</v>
+        <v>500</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3925</v>
+        <v>2474</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>تأخير لمدة 5 دقيقة يوم 2026-07-16
-مراجعة يوم 2026-07-26 السبب Consecutive 'إنصراف' at 17:33 and 17:46
-Achieved 55.0% of target (&lt;60%) → 0
-zero accepts deductions: 0.75</t>
+          <t>غياب يوم 2026-08-04 خصم 96 من الاساسي غياب يوم باذن خصم 96
+غياب يوم 2026-08-18 خصم 2 نقاط و192 من الاساسي غياب يوم بدون اذن خصم 192 ونقطتين
+غياب يوم 2026-08-29 خصم 96 من الاساسي غياب يوم باذن خصم 96
+غياب يوم 2026-08-30 خصم 2 نقاط و192 من الاساسي غياب يوم بدون اذن خصم 192 ونقطتين
+تأخير لمدة 5 دقيقة يوم 2026-08-09 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+مراجعة يوم 2026-08-16 السبب Consecutive 'حضور' at 08:33 and 17:31
+مراجعة يوم 2026-09-01
+خصم 450 السبب سلفة بتاريخ 27 - 8 قدرها 450 جنيه
+Achieved 47.5% of target (&lt;60%) → 0
+zero accepts deductions: 3.0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>maiyaser</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1135,39 +1126,47 @@
         <v>3000</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3000</v>
+        <v>1992</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="H13" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3900</v>
+        <v>1992</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-01
-غياب يوم 2026-07-02
-مراجعة يوم 2026-07-07 السبب Consecutive 'حضور' at 08:28 and 17:30
-مراجعة يوم 2026-07-08 السبب Consecutive 'إنصراف' at 17:34 and 17:44
-Active count 6 &lt; 25 → 0
-zero accepts deductions: 1.0</t>
+          <t>غياب يوم 2026-08-02 خصم 96 من الاساسي غياب يوم باذن خصم 96
+غياب يوم 2026-08-19 خصم 2 نقاط و192 من الاساسي غياب بدون اذن خصم 192 ونقطتين
+غياب يوم 2026-08-20 خصم 2 نقاط و192 من الاساسي غياب بدون اذن خصم 192 ونقطتين
+غياب يوم 2026-08-22 خصم 2 نقاط و192 من الاساسي غياب بدون اذن خصم 192 ونقطتين
+غياب يوم 2026-08-29 خصم 96 من الاساسي غياب يوم باذن خصم 96
+غياب يوم 2026-08-30 خصم 1 نقاط و192 من الاساسي غياب بدون اذن خصم 192 ونقطتين
+تأخير لمدة 21 دقيقة يوم 2026-08-17 خصم 0.5 نقاط تاخير نصف ساعه خصم نصف نقطه
+مراجعة يوم 2026-09-01
+خصم 48 السبب اذن نصف يوم خصم 48 جنيه
+خصم 2 نقطة السبب خصم الكواليتي بالكامل لتخطي ايام الغياب
+Achieved 57.5% of target (&lt;60%) → 0
+zero accepts deductions: 2.0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>nadamohammed</t>
+          <t>entesarmahmoud</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1192,11 +1191,9 @@
       <c r="G14" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J14" s="2" t="n">
         <v>0</v>
@@ -1206,17 +1203,16 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-06
-غياب يوم 2026-07-23
-تأخير لمدة 22 دقيقة يوم 2026-07-09
-zero accepts deductions: 0</t>
+          <t>مراجعة يوم 2026-09-01
+Active count nan outside ranges → 0
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>maiyaser</t>
+          <t>maysaa</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1239,36 +1235,30 @@
         <v>1000</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>975</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>35</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n">
-        <v>27</v>
+        <v/>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5175</v>
+        <v>4000</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-05
-غياب يوم 2026-07-09
-غياب يوم 2026-07-21
-تأخير لمدة 24 دقيقة يوم 2026-07-07
-تأخير لمدة 63 دقيقة يوم 2026-07-13
-Achieved 77.1% of target (60%–&lt;80%) → 2000 × 0.6 = 1200
-zero accepts deductions: 0.25</t>
+          <t>مراجعة يوم 2026-09-01
+Active count nan outside ranges → 0
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>nourgamal</t>
+          <t>salwahassan</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1285,57 +1275,41 @@
         <v>3000</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3000</v>
+        <v>2520</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4000</v>
+        <v>3320</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-08
-غياب يوم 2026-07-09
-غياب يوم 2026-07-11
-غياب يوم 2026-07-12
-غياب يوم 2026-07-13
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-غياب يوم 2026-07-26
-غياب يوم 2026-07-27
-غياب يوم 2026-07-28
-غياب يوم 2026-07-29
-غياب يوم 2026-07-30
-تأخير لمدة 17 دقيقة يوم 2026-07-02
-zero accepts deductions: 0</t>
+          <t>غياب يوم 2026-08-10 خصم 96 من الاساسي غياب يوم باذن خصم 96
+غياب يوم 2026-08-22 خصم 96 من الاساسي غياب يوم باذن خصم 96
+غياب يوم 2026-08-29 خصم 2 نقاط و192 من الاساسي غياب يوم بدون اذن خصم 192 ونقطتين
+تأخير لمدة 244 دقيقة يوم 2026-08-18
+مراجعة يوم 2026-09-01
+خصم 96 السبب غياب نصف يوم بتاريخ 18 - 8 مع تعدي حد الغياب المسموح خصم 96 جنيه
+Active count nan outside ranges → 0
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>entesarmahmoud</t>
+          <t>habibaalaa</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1345,42 +1319,46 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3000</v>
+        <v>1354.838709677419</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3000</v>
+        <v>970.8387096774193</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1000</v>
+        <v>451.6129032258065</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>875</v>
+        <v>26.61290322580646</v>
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v/>
       </c>
       <c r="J17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3875</v>
+        <v>997.4516129032259</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Active count 7 &lt; 25 → 0
-zero accepts deductions: 1.25</t>
+          <t>غياب يوم 2026-08-02 خصم 2 نقاط و192 من الاساسي غياب يوم بدون اذن خصم 192 ونقطتين
+غياب يوم 2026-08-08 خصم 2 نقاط و192 من الاساسي غياب يوم بدون اذن خصم 192 و نقطتين
+تأخير لمدة 7 دقيقة يوم 2026-08-04 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+مراجعة يوم 2026-08-01
+Active count nan outside ranges → 0
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>rehabhassan</t>
+          <t>shahendaalaa</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1397,56 +1375,53 @@
         <v>3000</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3000</v>
+        <v>2904</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v/>
+        <v>40</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4000</v>
+        <v>3304</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-08
-غياب يوم 2026-07-11
-غياب يوم 2026-07-12
-غياب يوم 2026-07-13
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-غياب يوم 2026-07-26
-غياب يوم 2026-07-27
-غياب يوم 2026-07-28
-غياب يوم 2026-07-29
-غياب يوم 2026-07-30
-Target is zero or invalid → 0
-zero accepts deductions: 0</t>
+          <t>غياب يوم 2026-08-10 خصم 96 من الاساسي غياب يوم باذن خصم 96
+تأخير لمدة 23 دقيقة يوم 2026-08-05 خصم 0.5 نقاط تاخير نصف ساعه خصم نصف نقطة
+تأخير لمدة 6 دقيقة يوم 2026-08-06 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه 
+تأخير لمدة 2 دقيقة يوم 2026-08-09
+تأخير لمدة 16 دقيقة يوم 2026-08-12 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 94 دقيقة يوم 2026-08-13 خصم 1.5 نقاط تاخير ساعه ونصف خصم نقطه ونصف
+تأخير لمدة 4 دقيقة يوم 2026-08-16
+تأخير لمدة 6 دقيقة يوم 2026-08-18
+تأخير لمدة 4 دقيقة يوم 2026-08-19
+تأخير لمدة 15 دقيقة يوم 2026-08-22 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 11 دقيقة يوم 2026-08-25 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 16 دقيقة يوم 2026-08-29 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 10 دقيقة يوم 2026-08-31 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 13 دقيقة يوم 2026-09-01
+مراجعة يوم 2026-08-13
+مراجعة يوم 2026-09-01
+Achieved 17.5% of target (&lt;60%) → 0
+zero accepts deductions: 10.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>maysaa</t>
+          <t>nourmohsen</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1463,37 +1438,43 @@
         <v>3000</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3000</v>
+        <v>2904</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>875</v>
-      </c>
-      <c r="H19" s="2" t="n"/>
+        <v>775</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3875</v>
+        <v>3679</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>تأخير لمدة 530 دقيقة يوم 2026-07-08
-مراجعة يوم 2026-07-08
-Active count 10 &lt; 25 → 0
-zero accepts deductions: 1.25</t>
+          <t>غياب يوم 2026-08-29 خصم 96 من الاساسي غياب يوم باذن خصم 96 جنيه
+تأخير لمدة 10 دقيقة يوم 2026-08-04 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطة
+تأخير لمدة 1 دقيقة يوم 2026-08-09
+تأخير لمدة 5 دقيقة يوم 2026-08-25 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+مراجعة يوم 2026-08-13 السبب Consecutive 'حضور' at 08:31 and 15:01
+مراجعة يوم 2026-09-01
+Achieved 32.5% of target (&lt;60%) → 0
+zero accepts deductions: 7.0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>salwahassan</t>
+          <t>gehad</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1518,9 +1499,11 @@
       <c r="G20" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="H20" s="2" t="n"/>
+      <c r="H20" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0</v>
@@ -1530,19 +1513,20 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-19
-تأخير لمدة 2 دقيقة يوم 2026-07-20
-مراجعة يوم 2026-07-05
-مراجعة يوم 2026-07-26 السبب Consecutive 'حضور' at 08:38 and 12:12
-Active count 2 &lt; 25 → 0
-zero accepts deductions: 2.0</t>
+          <t>تأخير لمدة 10 دقيقة يوم 2026-08-04 تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 1 دقيقة يوم 2026-08-09
+تأخير لمدة 5 دقيقة يوم 2026-08-25
+مراجعة يوم 2026-09-01
+خصم 1 نقطة السبب fake offer ( 15 - 8 - 2026 )
+Achieved 45.0% of target (&lt;60%) → 0
+zero accepts deductions: 4.0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>habibaalaa</t>
+          <t>shahdfarrag</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1552,52 +1536,46 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3000</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3000</v>
+        <v>582.9677419354839</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1000</v>
+        <v>290.3225806451613</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>875</v>
+        <v>65.32258064516134</v>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3875</v>
+        <v>648.2903225806452</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-01
-غياب يوم 2026-07-02
-غياب يوم 2026-07-04
-غياب يوم 2026-07-05
-غياب يوم 2026-07-12
-غياب يوم 2026-07-23
-مراجعة يوم 2026-07-06
-مراجعة يوم 2026-07-07 السبب Consecutive 'حضور' at 08:29 and 17:28
-مراجعة يوم 2026-07-08 السبب Consecutive 'حضور' at 08:26 and 17:30
-مراجعة يوم 2026-07-09 السبب Consecutive 'حضور' at 08:27 and 12:59
-Active count 0 &lt; 25 → 0
-zero accepts deductions: 1.25</t>
+          <t>غياب يوم 2026-08-01 خصم 96 من الاساسي غياب يوم باذن خصم 96
+غياب يوم 2026-08-05 خصم 2 نقاط و192 من الاساسي غياب يوم بدون اذن خصم 192 ونقطتين
+تأخير لمدة 2 دقيقة يوم 2026-08-02
+تأخير لمدة 7 دقيقة يوم 2026-08-04 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+Active count nan outside ranges → 0
+zero accepts deductions: 0.0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>shahendaalaa</t>
+          <t>malakmahmoud</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1614,54 +1592,52 @@
         <v>3000</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3000</v>
+        <v>2904</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>825</v>
+        <v>700</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>35</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3825</v>
+        <v>4804</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-01
-غياب يوم 2026-07-02
-غياب يوم 2026-07-04
-غياب يوم 2026-07-05
-غياب يوم 2026-07-06
-غياب يوم 2026-07-07
-غياب يوم 2026-07-08
-غياب يوم 2026-07-21
-تأخير لمدة 15 دقيقة يوم 2026-07-13
-تأخير لمدة 3 دقيقة يوم 2026-07-16
-تأخير لمدة 96 دقيقة يوم 2026-07-18
-تأخير لمدة 9 دقيقة يوم 2026-07-19
-تأخير لمدة 1 دقيقة يوم 2026-07-20
-تأخير لمدة 8 دقيقة يوم 2026-07-25
-مراجعة يوم 2026-07-09
-مراجعة يوم 2026-07-23 السبب Consecutive 'حضور' at 08:33 and 17:30
-مراجعة يوم 2026-07-30 السبب Consecutive 'حضور' at 08:29 and 15:26
-Achieved 11.4% of target (&lt;60%) → 0
-zero accepts deductions: 1.75</t>
+          <t>غياب يوم 2026-08-10 خصم 96 من الاساسي غياب يوم باذن خصم 96 جنيه
+تأخير لمدة 4 دقيقة يوم 2026-08-05
+تأخير لمدة 1 دقيقة يوم 2026-08-06
+تأخير لمدة 1 دقيقة يوم 2026-08-08
+تأخير لمدة 1 دقيقة يوم 2026-08-09
+تأخير لمدة 8 دقيقة يوم 2026-08-13 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 7 دقيقة يوم 2026-08-15 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 18 دقيقة يوم 2026-08-16 خصم 0.5 نقاط تاخير نصف ساعه خصم نصف نقطه
+تأخير لمدة 4 دقيقة يوم 2026-08-25 خصم 0.25 نقاط تاخير ربع ساعه خصم ربع نقطه
+تأخير لمدة 2 دقيقة يوم 2026-08-26
+تأخير لمدة 2 دقيقة يوم 2026-08-31
+تأخير لمدة 2 دقيقة يوم 2026-09-01
+مراجعة يوم 2026-08-25
+مراجعة يوم 2026-09-01
+خصم 1 نقطة السبب عدم متابعه مع العميل خصم نقطة بتاريخ 19 - 8
+Achieved 77.1% of target (60%–&lt;80%) → 2000 × 0.6 = 1200
+zero accepts deductions: 3.0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>nourmohsen</t>
+          <t>sarafathy</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1687,10 +1663,10 @@
         <v>975</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0</v>
@@ -1700,38 +1676,18 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-01
-غياب يوم 2026-07-02
-غياب يوم 2026-07-04
-غياب يوم 2026-07-05
-غياب يوم 2026-07-06
-غياب يوم 2026-07-07
-غياب يوم 2026-07-08
-غياب يوم 2026-07-09
-غياب يوم 2026-07-11
-غياب يوم 2026-07-12
-غياب يوم 2026-07-13
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-غياب يوم 2026-07-27
-مراجعة يوم 2026-07-26
-Achieved 13.3% of target (&lt;60%) → 0
-zero accepts deductions: 0.25</t>
+          <t>مراجعة يوم 2026-08-15
+مراجعة يوم 2026-08-31 السبب Consecutive 'حضور' at 13:11 and 17:37
+مراجعة يوم 2026-09-01
+Achieved 37.1% of target (&lt;60%) → 0
+zero accepts deductions: 1.0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>gehad</t>
+          <t>marwamahmoud</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1754,239 +1710,25 @@
         <v>1000</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>850</v>
+        <v>975</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3850</v>
+        <v>5175</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>غياب يوم 2026-07-01
-غياب يوم 2026-07-02
-غياب يوم 2026-07-04
-غياب يوم 2026-07-05
-غياب يوم 2026-07-06
-غياب يوم 2026-07-07
-غياب يوم 2026-07-08
-غياب يوم 2026-07-09
-غياب يوم 2026-07-11
-غياب يوم 2026-07-12
-غياب يوم 2026-07-13
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-غياب يوم 2026-07-27
-تأخير لمدة 1 دقيقة يوم 2026-07-30
-مراجعة يوم 2026-07-26
-Achieved 10.0% of target (&lt;60%) → 0
-zero accepts deductions: 1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>malakmahmoud</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>غياب يوم 2026-07-01
-غياب يوم 2026-07-02
-غياب يوم 2026-07-04
-غياب يوم 2026-07-05
-غياب يوم 2026-07-06
-غياب يوم 2026-07-07
-غياب يوم 2026-07-08
-غياب يوم 2026-07-09
-غياب يوم 2026-07-11
-غياب يوم 2026-07-12
-غياب يوم 2026-07-13
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-مراجعة يوم 2026-07-26
-مراجعة يوم 2026-07-28
-Target is zero or invalid → 0
-zero accepts deductions: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>sarafathy</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>967.741935483871</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>467.741935483871</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>322.5806451612903</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>322.5806451612903</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>790.3225806451612</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>مراجعة يوم 2026-07-26
-اضافة 100 السبب تعويض
-خصم 600 السبب سوء سلوك
-Achieved 3.3% of target (&lt;60%) → 0
-work days: 10
-zero accepts deductions: 0.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>marwamahmoud</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>975</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>3975</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>غياب يوم 2026-07-01
-غياب يوم 2026-07-02
-غياب يوم 2026-07-04
-غياب يوم 2026-07-05
-غياب يوم 2026-07-06
-غياب يوم 2026-07-07
-غياب يوم 2026-07-08
-غياب يوم 2026-07-09
-غياب يوم 2026-07-11
-غياب يوم 2026-07-12
-غياب يوم 2026-07-13
-غياب يوم 2026-07-14
-غياب يوم 2026-07-15
-غياب يوم 2026-07-16
-غياب يوم 2026-07-18
-غياب يوم 2026-07-19
-غياب يوم 2026-07-20
-غياب يوم 2026-07-21
-غياب يوم 2026-07-22
-غياب يوم 2026-07-23
-غياب يوم 2026-07-25
-غياب يوم 2026-07-26
-مراجعة يوم 2026-07-27
-Achieved 10.0% of target (&lt;60%) → 0
-zero accepts deductions: 0.25</t>
+          <t>تأخير لمدة 3 دقيقة يوم 2026-08-18
+Achieved 71.4% of target (60%–&lt;80%) → 2000 × 0.6 = 1200
+zero accepts deductions: 1.0</t>
         </is>
       </c>
     </row>
